--- a/bases/Wim_Du/projects/IMDEV-8927/Тестирование/ТаблицаОбработок.xlsx
+++ b/bases/Wim_Du/projects/IMDEV-8927/Тестирование/ТаблицаОбработок.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="8760"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="74">
   <si>
     <t>внИсполнениеСделокТ+2_ДУ_epf/</t>
   </si>
@@ -244,12 +244,27 @@
   <si>
     <t>1.42</t>
   </si>
+  <si>
+    <t>Пакетный отчет брокера ДУ</t>
+  </si>
+  <si>
+    <t>внПакетныйОтчетБрокераДУ_ДВО_epf/</t>
+  </si>
+  <si>
+    <t>На ПРОД старая версия! Взять ту что в GIT</t>
+  </si>
+  <si>
+    <t>2.41</t>
+  </si>
+  <si>
+    <t>???</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="10">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -316,6 +331,21 @@
       <strike/>
       <sz val="11"/>
       <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -440,7 +470,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -495,6 +525,26 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -776,7 +826,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:J21"/>
+  <dimension ref="A3:J22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -870,117 +920,121 @@
       <c r="J5" s="21"/>
     </row>
     <row r="6" spans="1:10" ht="17.25" thickBot="1">
-      <c r="A6" s="6">
+      <c r="A6" s="25">
         <v>3</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="26">
         <v>3</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="H6" s="8"/>
-      <c r="I6" s="1" t="s">
+      <c r="G6" s="25"/>
+      <c r="H6" s="30"/>
+      <c r="I6" s="28" t="s">
         <v>35</v>
       </c>
       <c r="J6" s="21"/>
     </row>
     <row r="7" spans="1:10" ht="17.25" thickBot="1">
-      <c r="A7" s="6">
-        <v>4</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>15</v>
+      <c r="A7" s="31">
+        <v>3</v>
+      </c>
+      <c r="B7" s="2">
+        <v>3</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E7" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H7" s="8"/>
-      <c r="I7" s="1" t="s">
-        <v>43</v>
+        <v>70</v>
+      </c>
+      <c r="D7" s="32" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="G7" s="31"/>
+      <c r="H7" s="33"/>
+      <c r="I7" s="15" t="s">
+        <v>71</v>
       </c>
       <c r="J7" s="21"/>
     </row>
     <row r="8" spans="1:10" ht="17.25" thickBot="1">
       <c r="A8" s="6">
-        <v>5</v>
-      </c>
-      <c r="B8" s="2">
+        <v>4</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="10" t="s">
-        <v>4</v>
-      </c>
       <c r="D8" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E8" s="17" t="s">
-        <v>45</v>
+        <v>41</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>42</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H8" s="8"/>
+      <c r="I8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J8" s="21"/>
     </row>
     <row r="9" spans="1:10" ht="17.25" thickBot="1">
       <c r="A9" s="6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B9" s="2">
-        <v>5</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>5</v>
+        <v>3</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G9" s="22" t="s">
-        <v>27</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="H9" s="8"/>
     </row>
     <row r="10" spans="1:10" ht="17.25" thickBot="1">
       <c r="A10" s="6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B10" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G10" s="22" t="s">
         <v>27</v>
@@ -988,249 +1042,272 @@
     </row>
     <row r="11" spans="1:10" ht="17.25" thickBot="1">
       <c r="A11" s="6">
-        <v>8</v>
-      </c>
-      <c r="B11" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="10" t="s">
-        <v>8</v>
+      <c r="B11" s="2">
+        <v>6</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H11" s="8"/>
+        <v>45</v>
+      </c>
+      <c r="G11" s="22" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="12" spans="1:10" ht="17.25" thickBot="1">
       <c r="A12" s="6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>10</v>
+        <v>7</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>8</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E12" s="18" t="s">
-        <v>52</v>
+        <v>49</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>50</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="G12" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J12" s="21"/>
+        <v>50</v>
+      </c>
+      <c r="H12" s="8"/>
     </row>
     <row r="13" spans="1:10" ht="17.25" thickBot="1">
       <c r="A13" s="6">
+        <v>9</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="2">
-        <v>9</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>11</v>
-      </c>
       <c r="D13" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E13" s="17" t="s">
-        <v>47</v>
+        <v>51</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>52</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G13" s="22" t="s">
         <v>27</v>
       </c>
+      <c r="I13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J13" s="21"/>
     </row>
     <row r="14" spans="1:10" ht="17.25" thickBot="1">
       <c r="A14" s="6">
+        <v>10</v>
+      </c>
+      <c r="B14" s="2">
+        <v>9</v>
+      </c>
+      <c r="C14" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="2">
-        <v>11</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>12</v>
-      </c>
       <c r="D14" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="H14" s="8"/>
+        <v>47</v>
+      </c>
+      <c r="G14" s="22" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="15" spans="1:10" ht="17.25" thickBot="1">
       <c r="A15" s="6">
+        <v>11</v>
+      </c>
+      <c r="B15" s="2">
+        <v>11</v>
+      </c>
+      <c r="C15" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="2">
-        <v>12</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>13</v>
-      </c>
       <c r="D15" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="G15" s="22" t="s">
-        <v>27</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="H15" s="8"/>
     </row>
     <row r="16" spans="1:10" ht="17.25" thickBot="1">
       <c r="A16" s="6">
+        <v>12</v>
+      </c>
+      <c r="B16" s="2">
+        <v>12</v>
+      </c>
+      <c r="C16" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="2">
-        <v>14</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>14</v>
-      </c>
       <c r="D16" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H16" s="8"/>
+        <v>57</v>
+      </c>
+      <c r="G16" s="22" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="17" spans="1:8" ht="17.25" thickBot="1">
       <c r="A17" s="6">
+        <v>13</v>
+      </c>
+      <c r="B17" s="2">
         <v>14</v>
       </c>
-      <c r="B17" s="2">
-        <v>19</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>17</v>
+      <c r="C17" s="10" t="s">
+        <v>14</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="G17" s="22" t="s">
-        <v>27</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="H17" s="8"/>
     </row>
     <row r="18" spans="1:8" ht="17.25" thickBot="1">
       <c r="A18" s="6">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B18" s="2">
         <v>19</v>
       </c>
-      <c r="C18" s="10" t="s">
-        <v>16</v>
+      <c r="C18" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H18" s="8"/>
+        <v>61</v>
+      </c>
+      <c r="G18" s="22" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="19" spans="1:8" ht="17.25" thickBot="1">
       <c r="A19" s="6">
+        <v>15</v>
+      </c>
+      <c r="B19" s="2">
+        <v>19</v>
+      </c>
+      <c r="C19" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B19" s="2">
+      <c r="D19" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E19" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H19" s="8"/>
+    </row>
+    <row r="20" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A20" s="6">
+        <v>16</v>
+      </c>
+      <c r="B20" s="2">
         <v>20</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C20" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D20" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="E19" s="17" t="s">
+      <c r="E20" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="F20" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G19" s="22" t="s">
+      <c r="G20" s="22" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="17.25" thickBot="1">
-      <c r="A20" s="11">
+    <row r="21" spans="1:8" ht="17.25" thickBot="1">
+      <c r="A21" s="11">
         <v>17</v>
       </c>
-      <c r="B20" s="5">
+      <c r="B21" s="5">
         <v>20</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C21" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="D20" s="13" t="s">
+      <c r="D21" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="E20" s="19" t="s">
+      <c r="E21" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="F20" s="13" t="s">
+      <c r="F21" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="G20" s="11"/>
-      <c r="H20" s="14"/>
-    </row>
-    <row r="21" spans="1:8" ht="30.75" thickBot="1">
-      <c r="A21" s="6">
+      <c r="G21" s="11"/>
+      <c r="H21" s="14"/>
+    </row>
+    <row r="22" spans="1:8" ht="30.75" thickBot="1">
+      <c r="A22" s="6">
         <v>17</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B22" s="2">
         <v>20</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C22" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="D21" s="20" t="s">
+      <c r="D22" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="E21" s="17" t="s">
+      <c r="E22" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="F22" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="G21" s="22" t="s">
+      <c r="G22" s="22" t="s">
         <v>27</v>
       </c>
     </row>

--- a/bases/Wim_Du/projects/IMDEV-8927/Тестирование/ТаблицаОбработок.xlsx
+++ b/bases/Wim_Du/projects/IMDEV-8927/Тестирование/ТаблицаОбработок.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="8760"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24720" windowHeight="8760"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -520,12 +520,6 @@
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -545,6 +539,12 @@
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -859,10 +859,10 @@
       <c r="F3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="23" t="s">
+      <c r="G3" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="24"/>
+      <c r="H3" s="34"/>
       <c r="I3" s="16" t="s">
         <v>31</v>
       </c>
@@ -920,33 +920,33 @@
       <c r="J5" s="21"/>
     </row>
     <row r="6" spans="1:10" ht="17.25" thickBot="1">
-      <c r="A6" s="25">
+      <c r="A6" s="23">
         <v>3</v>
       </c>
-      <c r="B6" s="26">
+      <c r="B6" s="24">
         <v>3</v>
       </c>
-      <c r="C6" s="27" t="s">
+      <c r="C6" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="28" t="s">
+      <c r="D6" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="E6" s="29" t="s">
+      <c r="E6" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="28" t="s">
+      <c r="F6" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="G6" s="25"/>
-      <c r="H6" s="30"/>
-      <c r="I6" s="28" t="s">
+      <c r="G6" s="23"/>
+      <c r="H6" s="28"/>
+      <c r="I6" s="26" t="s">
         <v>35</v>
       </c>
       <c r="J6" s="21"/>
     </row>
     <row r="7" spans="1:10" ht="17.25" thickBot="1">
-      <c r="A7" s="31">
+      <c r="A7" s="29">
         <v>3</v>
       </c>
       <c r="B7" s="2">
@@ -955,17 +955,17 @@
       <c r="C7" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="D7" s="32" t="s">
+      <c r="D7" s="30" t="s">
         <v>69</v>
       </c>
-      <c r="E7" s="34" t="s">
+      <c r="E7" s="32" t="s">
         <v>72</v>
       </c>
       <c r="F7" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="G7" s="31"/>
-      <c r="H7" s="33"/>
+      <c r="G7" s="29"/>
+      <c r="H7" s="31"/>
       <c r="I7" s="15" t="s">
         <v>71</v>
       </c>
